--- a/artfynd/A 4164-2023 artfynd.xlsx
+++ b/artfynd/A 4164-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4164-2023 artfynd.xlsx
+++ b/artfynd/A 4164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5039756</v>
+        <v>2153599</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609721.785717515</v>
+        <v>609687</v>
       </c>
       <c r="R2" t="n">
-        <v>6300380.50981768</v>
+        <v>6300312</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,41 +773,40 @@
           <t>Åke Rühling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2153599</v>
+        <v>4529521</v>
       </c>
       <c r="B3" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609687.3836769508</v>
+        <v>609665</v>
       </c>
       <c r="R3" t="n">
-        <v>6300312.287732385</v>
+        <v>6300467</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,21 +849,11 @@
           <t>2008-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-07-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +865,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Talldunge</t>
+          <t>Markväg och kanter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,7 +879,330 @@
           <t>Åke Rühling</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4530744</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100292</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222223</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kösa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Apera spica-venti</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P. Beauv.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skedstad, SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>609631</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6300304</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bredsätra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sandig vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5039756</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skedstad, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>609722</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6300381</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bredsätra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Talldunge</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2582533</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108206</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223701</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig klofibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis tectorum var. tectorum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skedstad, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>609665</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6300467</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bredsätra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2008-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2008-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Markväg och kanter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4164-2023 artfynd.xlsx
+++ b/artfynd/A 4164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2153599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4529521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4530744</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5039756</t>
         </is>
       </c>
     </row>
@@ -1203,8 +1228,20 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2582533</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>